--- a/BWI/bestwine_output/bestwine_Ghana.xlsx
+++ b/BWI/bestwine_output/bestwine_Ghana.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA26"/>
+  <dimension ref="A1:AA30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3201,6 +3201,410 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Imexco Ghana Limited</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Imexco Ghana Limited</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>51778</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Accra</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Greater Accra Region, Accra Metropolis</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Po Box Tf 190</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>https://imexcogh.com</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>info@imexcoghana.com</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>C-39628</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/imexco-ghana-ltd/</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/imexcodrinksgh/</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/imexcodrinksgh/</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>Feghali Jean Paul</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/feghali-jean-paul-a802a6105/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Imexco Ghana Limited</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Imexco Ghana Limited</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>51778</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Accra</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Greater Accra Region, Accra Metropolis</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Po Box Tf 190</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://imexcogh.com</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>info@imexcoghana.com</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>C-39628</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/imexco-ghana-ltd/</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/imexcodrinksgh/</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/imexcodrinksgh/</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>Hamid Mahmood</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hamid-mahmood-907b8166/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Imexco Ghana Limited</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Imexco Ghana Limited</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>51778</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Accra</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Greater Accra Region, Accra Metropolis</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Po Box Tf 190</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>https://imexcogh.com</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>info@imexcoghana.com</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>C-39628</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/imexco-ghana-ltd/</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/imexcodrinksgh/</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/imexcodrinksgh/</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>Irene Boakye</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Manager</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/irene-boakye-aa76b9102/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Imexco Ghana Limited</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Imexco Ghana Limited</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>51778</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Accra</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Greater Accra Region, Accra Metropolis</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Po Box Tf 190</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://imexcogh.com</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>info@imexcoghana.com</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>C-39628</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/imexco-ghana-ltd/</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/imexcodrinksgh/</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/imexcodrinksgh/</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>Carl - Martin Senu</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carl-martin-senu-787a649b/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
